--- a/artfynd/A 1396-2022 artfynd.xlsx
+++ b/artfynd/A 1396-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -955,6 +955,147 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>123765166</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58319</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ämsjön SO, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>617373</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6648412</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vittinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>21:11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-03</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>21:11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>ute och knallar</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Väg</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>grusväg genom barrskog/hygge</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Gabriel Tjernberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Gabriel Tjernberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 1396-2022 artfynd.xlsx
+++ b/artfynd/A 1396-2022 artfynd.xlsx
@@ -960,7 +960,7 @@
         <v>123765166</v>
       </c>
       <c r="B4" t="n">
-        <v>58319</v>
+        <v>58322</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 1396-2022 artfynd.xlsx
+++ b/artfynd/A 1396-2022 artfynd.xlsx
@@ -960,7 +960,7 @@
         <v>123765166</v>
       </c>
       <c r="B4" t="n">
-        <v>58322</v>
+        <v>58323</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 1396-2022 artfynd.xlsx
+++ b/artfynd/A 1396-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>116517843</v>
+        <v>130292067</v>
       </c>
       <c r="B2" t="n">
-        <v>58090</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57144</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,50 +686,49 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208249</v>
+        <v>102613</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sörviken O, Upl</t>
+          <t>Heby, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>617374</v>
+        <v>617397</v>
       </c>
       <c r="R2" t="n">
-        <v>6648395</v>
+        <v>6648384</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -758,27 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2025-12-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2025-12-25</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>22:50</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>vattenansamling på hygge</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,44 +776,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>hygge</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Gabriel Tjernberg</t>
+          <t>Annika Bergquist</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Gabriel Tjernberg, Nike Nylander</t>
+          <t>Annika Bergquist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>116517836</v>
+        <v>123765166</v>
       </c>
       <c r="B3" t="n">
-        <v>58088</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -832,21 +805,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208250</v>
+        <v>208245</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -859,20 +832,20 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sörviken O, Upl</t>
+          <t>Ämsjön SO, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>617374</v>
+        <v>617373</v>
       </c>
       <c r="R3" t="n">
-        <v>6648395</v>
+        <v>6648412</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -899,27 +872,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2025-04-03</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>22:50</t>
+          <t>21:11</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>vattenansamling på hygge</t>
+          <t>ute och knallar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -934,12 +907,12 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Väg</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>hygge</t>
+          <t>grusväg genom barrskog/hygge</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -950,22 +923,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Gabriel Tjernberg, Nike Nylander</t>
+          <t>Gabriel Tjernberg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123765166</v>
+        <v>116517843</v>
       </c>
       <c r="B4" t="n">
-        <v>58345</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58817</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,26 +941,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>208245</v>
+        <v>208249</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr"/>
@@ -1000,20 +968,20 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ämsjön SO, Upl</t>
+          <t>Sörviken O, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>617373</v>
+        <v>617374</v>
       </c>
       <c r="R4" t="n">
-        <v>6648412</v>
+        <v>6648395</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1040,27 +1008,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>21:11</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-03</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>21:11</t>
+          <t>22:50</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>ute och knallar</t>
+          <t>vattenansamling på hygge</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1075,12 +1043,12 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Väg</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>grusväg genom barrskog/hygge</t>
+          <t>hygge</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1091,10 +1059,146 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
+          <t>Gabriel Tjernberg, Nike Nylander</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>116517836</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58815</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sörviken O, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>617374</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6648395</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vittinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>22:50</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-05-01</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>22:50</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>vattenansamling på hygge</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>hygge</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
           <t>Gabriel Tjernberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Gabriel Tjernberg, Nike Nylander</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 1396-2022 artfynd.xlsx
+++ b/artfynd/A 1396-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130292067</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -927,6 +937,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123765166</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1063,6 +1078,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116517843</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1199,8 +1219,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116517836</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>